--- a/信息工程系见习岗人名单20260316.xlsx
+++ b/信息工程系见习岗人名单20260316.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="24000" windowHeight="9720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>序号</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>陈思文</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>关天昊</t>
   </si>
 </sst>
 </file>
@@ -1242,8 +1248,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.4" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="13.6666666666667" style="1" customWidth="1"/>
@@ -1259,7 +1265,7 @@
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -1268,9 +1274,9 @@
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
@@ -1279,9 +1285,9 @@
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
@@ -1290,9 +1296,9 @@
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
@@ -1301,9 +1307,20 @@
       <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
